--- a/exports/trend_1d/KPITTECH_full_report.xlsx
+++ b/exports/trend_1d/KPITTECH_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:U50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>19.26</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43663</v>
+        <v>43664</v>
       </c>
       <c r="H2" t="n">
-        <v>88.05</v>
+        <v>86.2</v>
       </c>
       <c r="I2" t="n">
         <v>87.10291564672423</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K2" t="n">
-        <v>-8.279999999999999</v>
+        <v>-10.21</v>
       </c>
       <c r="L2" t="n">
-        <v>11.25</v>
+        <v>11.46</v>
       </c>
       <c r="M2" t="n">
         <v>2.94</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>14.09</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43703</v>
+        <v>43704</v>
       </c>
       <c r="H3" t="n">
-        <v>91.09999999999999</v>
+        <v>95.05</v>
       </c>
       <c r="I3" t="n">
         <v>92.50969415664268</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.68</v>
+        <v>-10.27</v>
       </c>
       <c r="L3" t="n">
-        <v>10.09</v>
+        <v>14.85</v>
       </c>
       <c r="M3" t="n">
         <v>3.23</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>17.59</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43810</v>
+        <v>43811</v>
       </c>
       <c r="H4" t="n">
-        <v>87.2</v>
+        <v>86.7</v>
       </c>
       <c r="I4" t="n">
         <v>87.18190702846501</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.26</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L4" t="n">
         <v>10.78</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>13.85</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43844</v>
+        <v>43845</v>
       </c>
       <c r="H5" t="n">
-        <v>97.95</v>
+        <v>102.35</v>
       </c>
       <c r="I5" t="n">
         <v>98.36490876042834</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K5" t="n">
-        <v>-12.98</v>
+        <v>-18.05</v>
       </c>
       <c r="L5" t="n">
-        <v>15.92</v>
+        <v>21.28</v>
       </c>
       <c r="M5" t="n">
         <v>2.13</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>14.3</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43872</v>
+        <v>43873</v>
       </c>
       <c r="H6" t="n">
-        <v>95.15000000000001</v>
+        <v>91.05</v>
       </c>
       <c r="I6" t="n">
         <v>92.04044812344921</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.03</v>
+        <v>-11.04</v>
       </c>
       <c r="L6" t="n">
-        <v>8.35</v>
+        <v>11.82</v>
       </c>
       <c r="M6" t="n">
         <v>2.36</v>
       </c>
       <c r="N6" t="n">
-        <v>3.91</v>
+        <v>4.31</v>
       </c>
       <c r="O6" t="n">
         <v>4.49</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>19.37</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43949</v>
+        <v>43950</v>
       </c>
       <c r="H7" t="n">
-        <v>50.85</v>
+        <v>53.1</v>
       </c>
       <c r="I7" t="n">
         <v>51.59621495415978</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7" t="n">
-        <v>44.15</v>
+        <v>41.68</v>
       </c>
       <c r="L7" t="n">
         <v>5.88</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>20.43</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43966</v>
+        <v>43969</v>
       </c>
       <c r="H8" t="n">
-        <v>49.5</v>
+        <v>47.05</v>
       </c>
       <c r="I8" t="n">
         <v>47.07148748097632</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>-6.78</v>
+        <v>-11.39</v>
       </c>
       <c r="L8" t="n">
-        <v>11.11</v>
+        <v>11.39</v>
       </c>
       <c r="M8" t="n">
         <v>4.93</v>
       </c>
       <c r="N8" t="n">
-        <v>4.89</v>
+        <v>4.95</v>
       </c>
       <c r="O8" t="n">
         <v>4.42</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>24.98</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H9" t="n">
-        <v>49.25</v>
+        <v>51.7</v>
       </c>
       <c r="I9" t="n">
         <v>50.90490667408358</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.68</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>5.84</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>4.9</v>
+        <v>4.97</v>
       </c>
       <c r="N9" t="n">
-        <v>4.92</v>
+        <v>4.97</v>
       </c>
       <c r="O9" t="n">
         <v>-4.95</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>17.65</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44130</v>
+        <v>44131</v>
       </c>
       <c r="H10" t="n">
-        <v>101.25</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>99.88528721601332</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K10" t="n">
-        <v>95.84</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>20.08</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44169</v>
+        <v>44172</v>
       </c>
       <c r="H11" t="n">
-        <v>108.1</v>
+        <v>114</v>
       </c>
       <c r="I11" t="n">
         <v>110.1213802231734</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.08</v>
+        <v>-15.04</v>
       </c>
       <c r="L11" t="n">
-        <v>13.37</v>
+        <v>16.2</v>
       </c>
       <c r="M11" t="n">
         <v>5.88</v>
       </c>
       <c r="N11" t="n">
-        <v>5.11</v>
+        <v>5.46</v>
       </c>
       <c r="O11" t="n">
         <v>-2.12</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>14.51</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H12" t="n">
-        <v>329.75</v>
+        <v>306.55</v>
       </c>
       <c r="I12" t="n">
         <v>320.1695020104127</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K12" t="n">
-        <v>189.25</v>
+        <v>168.9</v>
       </c>
       <c r="L12" t="n">
         <v>8.460000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>5.58</v>
       </c>
       <c r="N12" t="n">
         <v>10.66</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>218</v>
+        <v>219</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>17.19</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44504</v>
+        <v>44508</v>
       </c>
       <c r="H13" t="n">
-        <v>348.65</v>
+        <v>354.75</v>
       </c>
       <c r="I13" t="n">
         <v>354.5897887956365</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>-13.73</v>
+        <v>-15.72</v>
       </c>
       <c r="L13" t="n">
-        <v>14.92</v>
+        <v>16.46</v>
       </c>
       <c r="M13" t="n">
         <v>4.62</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>13.74</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44592</v>
+        <v>44593</v>
       </c>
       <c r="H14" t="n">
-        <v>646.25</v>
+        <v>622.9</v>
       </c>
       <c r="I14" t="n">
         <v>626.8307550474801</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K14" t="n">
-        <v>82.17</v>
+        <v>75.59</v>
       </c>
       <c r="L14" t="n">
         <v>2.64</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>22.4</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44712</v>
+        <v>44713</v>
       </c>
       <c r="H15" t="n">
-        <v>530.3</v>
+        <v>543.7</v>
       </c>
       <c r="I15" t="n">
         <v>532.4367980180284</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K15" t="n">
-        <v>14.87</v>
+        <v>12.71</v>
       </c>
       <c r="L15" t="n">
         <v>5.62</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>15.1</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44725</v>
+        <v>44726</v>
       </c>
       <c r="H16" t="n">
-        <v>487.2</v>
+        <v>470.35</v>
       </c>
       <c r="I16" t="n">
         <v>480.1618203245009</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K16" t="n">
-        <v>-10.39</v>
+        <v>-13.49</v>
       </c>
       <c r="L16" t="n">
-        <v>10.89</v>
+        <v>14.11</v>
       </c>
       <c r="M16" t="n">
         <v>4.14</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>17.4</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44770</v>
+        <v>44771</v>
       </c>
       <c r="H17" t="n">
-        <v>536</v>
+        <v>547.95</v>
       </c>
       <c r="I17" t="n">
         <v>536.5366839141291</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K17" t="n">
-        <v>-13.96</v>
+        <v>-16.5</v>
       </c>
       <c r="L17" t="n">
-        <v>15.87</v>
+        <v>19.36</v>
       </c>
       <c r="M17" t="n">
         <v>3.31</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.53</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H18" t="n">
-        <v>711.05</v>
+        <v>650.45</v>
       </c>
       <c r="I18" t="n">
         <v>665.4523668402262</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K18" t="n">
-        <v>29.77</v>
+        <v>18.71</v>
       </c>
       <c r="L18" t="n">
         <v>5.79</v>
@@ -1467,7 +1682,7 @@
         <v>4.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.57</v>
+        <v>8.52</v>
       </c>
       <c r="O18" t="n">
         <v>2.23</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>15.55</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44956</v>
+        <v>44957</v>
       </c>
       <c r="H19" t="n">
-        <v>709.3</v>
+        <v>762.9</v>
       </c>
       <c r="I19" t="n">
         <v>750.05440522733</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K19" t="n">
-        <v>-9.050000000000001</v>
+        <v>-17.29</v>
       </c>
       <c r="L19" t="n">
-        <v>16.01</v>
+        <v>18.74</v>
       </c>
       <c r="M19" t="n">
         <v>0.79</v>
       </c>
       <c r="N19" t="n">
-        <v>5.97</v>
+        <v>7.56</v>
       </c>
       <c r="O19" t="n">
         <v>-8.52</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>14.14</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H20" t="n">
-        <v>925.1</v>
+        <v>811.2</v>
       </c>
       <c r="I20" t="n">
         <v>823.6091799046441</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K20" t="n">
-        <v>21.26</v>
+        <v>6.33</v>
       </c>
       <c r="L20" t="n">
         <v>8.02</v>
@@ -1581,7 +1820,7 @@
         <v>0.99</v>
       </c>
       <c r="N20" t="n">
-        <v>4.11</v>
+        <v>12.31</v>
       </c>
       <c r="O20" t="n">
         <v>7.56</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>21.42</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45063</v>
+        <v>45064</v>
       </c>
       <c r="H21" t="n">
-        <v>933.15</v>
+        <v>941.05</v>
       </c>
       <c r="I21" t="n">
         <v>936.4027670645629</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.03</v>
+        <v>-16.01</v>
       </c>
       <c r="L21" t="n">
-        <v>17.11</v>
+        <v>17.71</v>
       </c>
       <c r="M21" t="n">
         <v>1.35</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.82</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45127</v>
+        <v>45128</v>
       </c>
       <c r="H22" t="n">
-        <v>1060.7</v>
+        <v>1000.9</v>
       </c>
       <c r="I22" t="n">
         <v>1033.619329440165</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K22" t="n">
-        <v>12.71</v>
+        <v>6.36</v>
       </c>
       <c r="L22" t="n">
         <v>3.11</v>
@@ -1695,7 +1958,7 @@
         <v>2.44</v>
       </c>
       <c r="N22" t="n">
-        <v>4.85</v>
+        <v>5.64</v>
       </c>
       <c r="O22" t="n">
         <v>0.85</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>12.96</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45141</v>
+        <v>45142</v>
       </c>
       <c r="H23" t="n">
-        <v>1081.2</v>
+        <v>1146.25</v>
       </c>
       <c r="I23" t="n">
         <v>1130.608184857003</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.02</v>
+        <v>-14.52</v>
       </c>
       <c r="L23" t="n">
-        <v>12.26</v>
+        <v>15.1</v>
       </c>
       <c r="M23" t="n">
         <v>3.16</v>
       </c>
       <c r="N23" t="n">
-        <v>5.58</v>
+        <v>6.02</v>
       </c>
       <c r="O23" t="n">
         <v>-5.64</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>13.54</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45189</v>
+        <v>45190</v>
       </c>
       <c r="H24" t="n">
-        <v>1128.8</v>
+        <v>1077.6</v>
       </c>
       <c r="I24" t="n">
         <v>1096.709446007959</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.52</v>
+        <v>-5.99</v>
       </c>
       <c r="L24" t="n">
-        <v>4.91</v>
+        <v>7.04</v>
       </c>
       <c r="M24" t="n">
-        <v>0.18</v>
+        <v>0.96</v>
       </c>
       <c r="N24" t="n">
-        <v>2.49</v>
+        <v>4.54</v>
       </c>
       <c r="O24" t="n">
         <v>6.02</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>11.38</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45209</v>
+        <v>45210</v>
       </c>
       <c r="H25" t="n">
-        <v>1165.05</v>
+        <v>1223.7</v>
       </c>
       <c r="I25" t="n">
         <v>1173.391836896076</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>-8.119999999999999</v>
+        <v>-13.56</v>
       </c>
       <c r="L25" t="n">
-        <v>9.039999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>3.84</v>
+        <v>5.03</v>
       </c>
       <c r="O25" t="n">
         <v>-4.54</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.61</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45315</v>
+        <v>45316</v>
       </c>
       <c r="H26" t="n">
-        <v>1506.55</v>
+        <v>1415.45</v>
       </c>
       <c r="I26" t="n">
         <v>1447.924573386984</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K26" t="n">
-        <v>23.11</v>
+        <v>15.67</v>
       </c>
       <c r="L26" t="n">
         <v>10.83</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>12.95</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="H27" t="n">
-        <v>1524.65</v>
+        <v>1577.1</v>
       </c>
       <c r="I27" t="n">
         <v>1564.463377185149</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.71</v>
+        <v>-11.42</v>
       </c>
       <c r="L27" t="n">
-        <v>10.21</v>
+        <v>12.83</v>
       </c>
       <c r="M27" t="n">
         <v>2.86</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>13.04</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="H28" t="n">
-        <v>1546.1</v>
+        <v>1493.35</v>
       </c>
       <c r="I28" t="n">
         <v>1530.216309037967</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.97</v>
+        <v>-5.31</v>
       </c>
       <c r="L28" t="n">
-        <v>3.24</v>
+        <v>6.08</v>
       </c>
       <c r="M28" t="n">
         <v>2.11</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>10.87</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45408</v>
+        <v>45411</v>
       </c>
       <c r="H29" t="n">
-        <v>1416.45</v>
+        <v>1508.5</v>
       </c>
       <c r="I29" t="n">
         <v>1498.328715695204</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K29" t="n">
-        <v>5.15</v>
+        <v>-1.01</v>
       </c>
       <c r="L29" t="n">
         <v>4.59</v>
@@ -2094,7 +2441,7 @@
         <v>1.67</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>6.5</v>
       </c>
       <c r="O29" t="n">
         <v>-3.41</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>13.26</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H30" t="n">
-        <v>1444.2</v>
+        <v>1381.75</v>
       </c>
       <c r="I30" t="n">
         <v>1431.161278315503</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.26</v>
+        <v>-8.4</v>
       </c>
       <c r="L30" t="n">
-        <v>6.73</v>
+        <v>14.28</v>
       </c>
       <c r="M30" t="n">
         <v>1.62</v>
       </c>
       <c r="N30" t="n">
-        <v>3.05</v>
+        <v>4.32</v>
       </c>
       <c r="O30" t="n">
         <v>6.5</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>13.29</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45463</v>
+        <v>45464</v>
       </c>
       <c r="H31" t="n">
-        <v>1552.6</v>
+        <v>1588.75</v>
       </c>
       <c r="I31" t="n">
         <v>1565.328484090731</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K31" t="n">
-        <v>-12.36</v>
+        <v>-14.98</v>
       </c>
       <c r="L31" t="n">
-        <v>12.92</v>
+        <v>18.59</v>
       </c>
       <c r="M31" t="n">
         <v>1.68</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45553</v>
+        <v>45554</v>
       </c>
       <c r="H32" t="n">
-        <v>1727.25</v>
+        <v>1676.45</v>
       </c>
       <c r="I32" t="n">
         <v>1684.051880603467</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K32" t="n">
-        <v>8.720000000000001</v>
+        <v>5.52</v>
       </c>
       <c r="L32" t="n">
         <v>2.44</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.97</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45630</v>
+        <v>45631</v>
       </c>
       <c r="H33" t="n">
-        <v>1457.15</v>
+        <v>1493.1</v>
       </c>
       <c r="I33" t="n">
         <v>1461.372193028955</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K33" t="n">
-        <v>13.08</v>
+        <v>10.94</v>
       </c>
       <c r="L33" t="n">
         <v>8.74</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>11.4</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H34" t="n">
-        <v>1430.15</v>
+        <v>1369.65</v>
       </c>
       <c r="I34" t="n">
         <v>1410.624770749182</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.22</v>
+        <v>-8.27</v>
       </c>
       <c r="L34" t="n">
-        <v>5.7</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M34" t="n">
         <v>3.66</v>
       </c>
       <c r="N34" t="n">
-        <v>4.09</v>
+        <v>4.23</v>
       </c>
       <c r="O34" t="n">
         <v>2.47</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>10.72</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45694</v>
+        <v>45695</v>
       </c>
       <c r="H35" t="n">
-        <v>1434.55</v>
+        <v>1447.8</v>
       </c>
       <c r="I35" t="n">
         <v>1435.534851241112</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.74</v>
+        <v>-5.71</v>
       </c>
       <c r="L35" t="n">
         <v>7.98</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>11.58</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45709</v>
+        <v>45712</v>
       </c>
       <c r="H36" t="n">
-        <v>1310.1</v>
+        <v>1281.7</v>
       </c>
       <c r="I36" t="n">
         <v>1282.784507343836</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K36" t="n">
-        <v>-9.51</v>
+        <v>-11.47</v>
       </c>
       <c r="L36" t="n">
-        <v>10.62</v>
+        <v>13.44</v>
       </c>
       <c r="M36" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="N36" t="n">
         <v>4.01</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>10.88</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H37" t="n">
-        <v>1323.4</v>
+        <v>1384.55</v>
       </c>
       <c r="I37" t="n">
         <v>1328.596728764198</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.25</v>
+        <v>-8.02</v>
       </c>
       <c r="L37" t="n">
-        <v>3.88</v>
+        <v>9.19</v>
       </c>
       <c r="M37" t="n">
         <v>1.42</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>12.89</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H38" t="n">
-        <v>1211.1</v>
+        <v>1134</v>
       </c>
       <c r="I38" t="n">
         <v>1209.887568473765</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K38" t="n">
-        <v>-12.53</v>
+        <v>-18.1</v>
       </c>
       <c r="L38" t="n">
-        <v>13.3</v>
+        <v>19.43</v>
       </c>
       <c r="M38" t="n">
         <v>2.32</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>19.08</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45775</v>
+        <v>45776</v>
       </c>
       <c r="H39" t="n">
-        <v>1231.2</v>
+        <v>1264.8</v>
       </c>
       <c r="I39" t="n">
         <v>1257.883602340664</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K39" t="n">
-        <v>-8.57</v>
+        <v>-11.53</v>
       </c>
       <c r="L39" t="n">
         <v>12.61</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>16.32</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45832</v>
+        <v>45833</v>
       </c>
       <c r="H40" t="n">
-        <v>1306.1</v>
+        <v>1295.4</v>
       </c>
       <c r="I40" t="n">
         <v>1297.692707523819</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K40" t="n">
-        <v>3.27</v>
+        <v>2.42</v>
       </c>
       <c r="L40" t="n">
         <v>5.69</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>10.26</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="H41" t="n">
-        <v>1240.4</v>
+        <v>1288.5</v>
       </c>
       <c r="I41" t="n">
         <v>1268.074015125092</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K41" t="n">
-        <v>4.25</v>
+        <v>0.53</v>
       </c>
       <c r="L41" t="n">
         <v>1.28</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H42" t="n">
-        <v>1255.7</v>
+        <v>1212.8</v>
       </c>
       <c r="I42" t="n">
         <v>1224.122933837614</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.55</v>
+        <v>-5.88</v>
       </c>
       <c r="L42" t="n">
-        <v>4.17</v>
+        <v>6.25</v>
       </c>
       <c r="M42" t="n">
         <v>2.19</v>
       </c>
       <c r="N42" t="n">
-        <v>2.11</v>
+        <v>3.42</v>
       </c>
       <c r="O42" t="n">
         <v>3.88</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.58</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="H43" t="n">
-        <v>1212.5</v>
+        <v>1244.3</v>
       </c>
       <c r="I43" t="n">
         <v>1227.450707025906</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K43" t="n">
-        <v>0.02</v>
+        <v>-2.6</v>
       </c>
       <c r="L43" t="n">
         <v>3.88</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="H44" t="n">
-        <v>1207.4</v>
+        <v>1176.3</v>
       </c>
       <c r="I44" t="n">
         <v>1181.510154161467</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.97</v>
+        <v>-5.46</v>
       </c>
       <c r="L44" t="n">
         <v>6.53</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="H45" t="n">
-        <v>728.65</v>
+        <v>746.25</v>
       </c>
       <c r="I45" t="n">
         <v>731.3224016101568</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K45" t="n">
-        <v>38.06</v>
+        <v>36.56</v>
       </c>
       <c r="L45" t="n">
         <v>5.64</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>11.58</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="H46" t="n">
-        <v>742.6</v>
+        <v>712.2</v>
       </c>
       <c r="I46" t="n">
         <v>715.2245180502792</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.49</v>
+        <v>-4.56</v>
       </c>
       <c r="L46" t="n">
         <v>7.52</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>12.68</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="H47" t="n">
-        <v>602.45</v>
+        <v>638.75</v>
       </c>
       <c r="I47" t="n">
         <v>607.3309418390943</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K47" t="n">
-        <v>15.41</v>
+        <v>10.31</v>
       </c>
       <c r="L47" t="n">
         <v>4.44</v>
       </c>
       <c r="M47" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="N47" t="n">
-        <v>5.86</v>
+        <v>6.03</v>
       </c>
       <c r="O47" t="n">
         <v>-4.09</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>11.97</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="H48" t="n">
-        <v>575.45</v>
+        <v>562.25</v>
       </c>
       <c r="I48" t="n">
         <v>564.4771686807543</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K48" t="n">
-        <v>-9.91</v>
+        <v>-11.98</v>
       </c>
       <c r="L48" t="n">
-        <v>9.98</v>
+        <v>12.33</v>
       </c>
       <c r="M48" t="n">
         <v>4.5</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="H49" t="n">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="I49" t="n">
         <v>532.2633465744082</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K49" t="n">
-        <v>6.45</v>
+        <v>1.29</v>
       </c>
       <c r="L49" t="n">
         <v>3.33</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3294,6 +3893,14 @@
       <c r="Q50" t="n">
         <v>8</v>
       </c>
+      <c r="R50" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6518,7 +7125,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.1</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="6">
@@ -6528,7 +7135,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -6538,7 +7145,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8">
@@ -6548,7 +7155,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -6558,7 +7165,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71.5</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="10">
@@ -6568,7 +7175,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109.9</v>
+        <v>110.9</v>
       </c>
     </row>
     <row r="11">
@@ -6608,7 +7215,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.91</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="15">
@@ -6618,7 +7225,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.64</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="16">
@@ -6628,7 +7235,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.19</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="17">
@@ -6638,7 +7245,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>189.25</v>
+        <v>168.9</v>
       </c>
     </row>
     <row r="18">
@@ -6648,7 +7255,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="19">
@@ -6658,7 +7265,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.199999999999999</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="20">
@@ -6668,7 +7275,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -6678,7 +7285,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.11</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="22">
@@ -6688,7 +7295,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -6698,7 +7305,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -6708,7 +7315,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="25">
@@ -6728,7 +7335,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.51</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="27">
@@ -6748,7 +7355,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
